--- a/data/baeckerei_2025/Anlagenbuchhaltung.xlsx
+++ b/data/baeckerei_2025/Anlagenbuchhaltung.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anlagenbuchhaltung" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hinweise" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Anlagenbuchhaltung" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Hinweise" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,14 +444,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bäckerei Hoffmann GmbH  |  Anlagenbuchhaltung  |  Geschäftsjahr 01.01.2025 – 31.12.2025</t>
+          <t>Muster Bäckerei GmbH  |  Anlagenbuchhaltung  |  Geschäftsjahr 01.01.2025 – 31.12.2025</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fiktiver Testfall – 8_AI_Accounting Showcase  |  Alle Beträge in EUR</t>
+          <t>Fiktiver Musterfall  |  Alle Beträge in EUR</t>
         </is>
       </c>
     </row>

--- a/data/baeckerei_2025/Anlagenbuchhaltung.xlsx
+++ b/data/baeckerei_2025/Anlagenbuchhaltung.xlsx
@@ -928,7 +928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -977,6 +977,23 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Technische Anlagen und Maschinen (Konto 0441)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Zugang Ofen 150.000 EUR: Lieferung am 28.12.2025, betriebsbereit ab Januar 2026. Planmäßige Abschreibung ab 2026, im Geschäftsjahr 2025 daher keine AfA.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
